--- a/AAII_Financials/Yearly/LANV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LANV_YR_FIN.xlsx
@@ -1025,7 +1025,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>439100</v>
+        <v>451600</v>
       </c>
       <c r="E17" s="3">
         <v>427000</v>
@@ -1064,7 +1064,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-156700</v>
+        <v>-169200</v>
       </c>
       <c r="E18" s="3">
         <v>-124900</v>
@@ -1120,7 +1120,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4400</v>
+        <v>-8000</v>
       </c>
       <c r="E20" s="3">
         <v>9400</v>
@@ -1588,7 +1588,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4400</v>
+        <v>8000</v>
       </c>
       <c r="E32" s="3">
         <v>-9400</v>
